--- a/data/trans_orig/P16A08-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A08-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>30944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18314</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39239</t>
+          <t>38785</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443675</t>
+          <t>442832</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>461646</t>
+          <t>462560</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>292068</t>
+          <t>291164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303049</t>
+          <t>302916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>741218</t>
+          <t>741672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762143</t>
+          <t>762418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37637</t>
+          <t>37939</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17154</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39050</t>
+          <t>39874</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359044</t>
+          <t>360421</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>334228</t>
+          <t>333926</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>355924</t>
+          <t>355828</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>699749</t>
+          <t>698925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721645</t>
+          <t>720411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23370</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27837</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519019</t>
+          <t>518036</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533923</t>
+          <t>534505</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159107</t>
+          <t>159282</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>682334</t>
+          <t>683183</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>699372</t>
+          <t>700068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43399</t>
+          <t>43228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>20583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41711</t>
+          <t>41551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46277</t>
+          <t>44291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77442</t>
+          <t>76317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1194935</t>
+          <t>1195106</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1219383</t>
+          <t>1218509</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>672574</t>
+          <t>672734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>693714</t>
+          <t>693702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1875178</t>
+          <t>1876303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1906343</t>
+          <t>1908329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11840</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>30923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36990</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>337697</t>
+          <t>337791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347566</t>
+          <t>347665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>538434</t>
+          <t>537829</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>556407</t>
+          <t>556370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>881299</t>
+          <t>881956</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>902411</t>
+          <t>902024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35148</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61357</t>
+          <t>61057</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39741</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67890</t>
+          <t>69496</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284148</t>
+          <t>284123</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>294672</t>
+          <t>294787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1187403</t>
+          <t>1187703</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1213612</t>
+          <t>1214788</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1479070</t>
+          <t>1477464</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1507219</t>
+          <t>1505945</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61055</t>
+          <t>61148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98951</t>
+          <t>97292</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111178</t>
+          <t>113163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156515</t>
+          <t>157795</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>183708</t>
+          <t>183915</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>243869</t>
+          <t>240965</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3170221</t>
+          <t>3171880</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3208117</t>
+          <t>3208024</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3221609</t>
+          <t>3220329</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3266946</t>
+          <t>3264961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6403427</t>
+          <t>6406331</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6463588</t>
+          <t>6463381</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28843</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,82 +3383,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17687</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10823</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>27386</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>36191</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>26046</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>49511</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>6,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17687</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10591</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27165</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,67%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>36191</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>25561</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>50306</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408368</t>
+          <t>409037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425817</t>
+          <t>425659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,82 +3496,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>295680</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>285981</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>302544</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>94,36%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>91,26%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>96,55%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>714386</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>701066</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>724531</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>93,4%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>295680</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>286202</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>302776</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,33%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>714386</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>700271</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>725016</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>95,18%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11083</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31863</t>
+          <t>32427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33356</t>
+          <t>33458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57854</t>
+          <t>58055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385155</t>
+          <t>384591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>405935</t>
+          <t>405876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>301959</t>
+          <t>301857</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>320383</t>
+          <t>319781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694479</t>
+          <t>694278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721967</t>
+          <t>723032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33404</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47492</t>
+          <t>48940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>592934</t>
+          <t>592043</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613991</t>
+          <t>614035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>236729</t>
+          <t>236339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250961</t>
+          <t>250726</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>836784</t>
+          <t>835336</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>861897</t>
+          <t>860957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18387</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39454</t>
+          <t>39890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42540</t>
+          <t>41849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71432</t>
+          <t>73041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65815</t>
+          <t>65144</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104497</t>
+          <t>103606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1117861</t>
+          <t>1117425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1138928</t>
+          <t>1139408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>695225</t>
+          <t>693616</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>724117</t>
+          <t>724808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1819476</t>
+          <t>1820367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1858158</t>
+          <t>1858829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24720</t>
+          <t>25387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>20775</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>44161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32286</t>
+          <t>33847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59960</t>
+          <t>60518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>485876</t>
+          <t>485209</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501916</t>
+          <t>502212</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>714655</t>
+          <t>714207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>737654</t>
+          <t>737593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1209004</t>
+          <t>1208446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1236678</t>
+          <t>1235117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>26495</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42839</t>
+          <t>41036</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71722</t>
+          <t>70221</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53825</t>
+          <t>56961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87658</t>
+          <t>90219</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241287</t>
+          <t>239346</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256983</t>
+          <t>256126</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1033534</t>
+          <t>1035035</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1062417</t>
+          <t>1064220</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1283440</t>
+          <t>1280879</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1317273</t>
+          <t>1314137</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94174</t>
+          <t>92705</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140681</t>
+          <t>140226</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169579</t>
+          <t>171851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>227983</t>
+          <t>225421</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>276782</t>
+          <t>275536</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>351286</t>
+          <t>347986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3273638</t>
+          <t>3274093</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3320145</t>
+          <t>3321614</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3308919</t>
+          <t>3311481</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3367323</t>
+          <t>3365051</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6599935</t>
+          <t>6603235</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6674439</t>
+          <t>6675685</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>24741</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26220</t>
+          <t>27467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>22070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45270</t>
+          <t>45430</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404882</t>
+          <t>404351</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420601</t>
+          <t>420471</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>320835</t>
+          <t>319588</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337860</t>
+          <t>337400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730877</t>
+          <t>730717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>753698</t>
+          <t>754077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>22328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31428</t>
+          <t>30794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24037</t>
+          <t>23550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48239</t>
+          <t>46474</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354450</t>
+          <t>354899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>369775</t>
+          <t>369637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340845</t>
+          <t>341479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359126</t>
+          <t>359564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>701261</t>
+          <t>703026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725463</t>
+          <t>725950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8041</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22630</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17055</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38039</t>
+          <t>37717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499794</t>
+          <t>500041</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515361</t>
+          <t>515475</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143493</t>
+          <t>143432</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158082</t>
+          <t>158260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649997</t>
+          <t>650319</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670981</t>
+          <t>670577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39654</t>
+          <t>40105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36831</t>
+          <t>37120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64422</t>
+          <t>66432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62662</t>
+          <t>61552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97344</t>
+          <t>97974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1109984</t>
+          <t>1109533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1130729</t>
+          <t>1131305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>761454</t>
+          <t>759444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>789045</t>
+          <t>788756</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1878170</t>
+          <t>1877540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1912852</t>
+          <t>1913962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>12408</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31006</t>
+          <t>30133</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53175</t>
+          <t>53299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44004</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74378</t>
+          <t>75113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>589700</t>
+          <t>590573</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>608013</t>
+          <t>608298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>685069</t>
+          <t>684945</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710661</t>
+          <t>710909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1284572</t>
+          <t>1283837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1314946</t>
+          <t>1314764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22635</t>
+          <t>23575</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37644</t>
+          <t>36954</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68608</t>
+          <t>66659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50629</t>
+          <t>50066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81883</t>
+          <t>81814</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264510</t>
+          <t>263570</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279238</t>
+          <t>279388</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1013417</t>
+          <t>1015366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1044381</t>
+          <t>1045071</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1287287</t>
+          <t>1287356</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1318541</t>
+          <t>1319104</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85699</t>
+          <t>85870</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127733</t>
+          <t>128308</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,82 +8076,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>189509</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>163757</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>219150</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>293745</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>261074</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>329811</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>3,77%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>189509</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>164577</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>221626</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>293745</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>261846</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>328132</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3257989</t>
+          <t>3257414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3300023</t>
+          <t>3299852</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,82 +8189,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3342087</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3312446</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3367839</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>94,63%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>93,79%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>95,36%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6623573</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6587507</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6656244</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>95,23%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>96,23%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3150</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3342087</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3309970</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3367019</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>94,63%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>95,34%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6623573</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6589186</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6655472</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30770</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35702</t>
+          <t>36204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29801</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58847</t>
+          <t>56324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>474442</t>
+          <t>474810</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>496732</t>
+          <t>496618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>411765</t>
+          <t>411263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430804</t>
+          <t>430365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>893832</t>
+          <t>896355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>922878</t>
+          <t>922858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25737</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>20521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>40012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32448</t>
+          <t>33033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58099</t>
+          <t>57513</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>426476</t>
+          <t>426780</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443263</t>
+          <t>443534</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343287</t>
+          <t>342568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361818</t>
+          <t>362059</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>776694</t>
+          <t>777280</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>802345</t>
+          <t>801760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34562</t>
+          <t>36863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14683</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44621</t>
+          <t>45091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633702</t>
+          <t>631401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662246</t>
+          <t>662980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152228</t>
+          <t>152641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161746</t>
+          <t>161665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>790554</t>
+          <t>790084</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>825124</t>
+          <t>823220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44911</t>
+          <t>45253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50222</t>
+          <t>50501</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44440</t>
+          <t>43790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84742</t>
+          <t>83226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>989908</t>
+          <t>989566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1014280</t>
+          <t>1014628</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>926975</t>
+          <t>926696</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>960588</t>
+          <t>960563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1927274</t>
+          <t>1928790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967576</t>
+          <t>1968226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29417</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>302081</t>
+          <t>294043</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>47258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>347114</t>
+          <t>308002</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>444027</t>
+          <t>444834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462107</t>
+          <t>462655</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>536915</t>
+          <t>544953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>809579</t>
+          <t>810079</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>965441</t>
+          <t>1004553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1266738</t>
+          <t>1265297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19787</t>
+          <t>20009</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39958</t>
+          <t>40276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59099</t>
+          <t>56739</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214900</t>
+          <t>211630</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237734</t>
+          <t>237743</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>720194</t>
+          <t>719876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>740365</t>
+          <t>740143</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>941560</t>
+          <t>943920</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>974401</t>
+          <t>974154</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81864</t>
+          <t>78842</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137087</t>
+          <t>139397</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147493</t>
+          <t>148888</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>460706</t>
+          <t>485790</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250076</t>
+          <t>250852</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>664764</t>
+          <t>633255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3237487</t>
+          <t>3235177</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3292710</t>
+          <t>3295732</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3112597</t>
+          <t>3087513</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3425810</t>
+          <t>3424415</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6283113</t>
+          <t>6314622</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6697801</t>
+          <t>6697025</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A08-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A08-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30944</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15516</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38785</t>
+          <t>41165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442832</t>
+          <t>444628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>462560</t>
+          <t>462228</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291164</t>
+          <t>292096</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302916</t>
+          <t>302834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>741672</t>
+          <t>739292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762418</t>
+          <t>762971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37939</t>
+          <t>36134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18388</t>
+          <t>18402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39874</t>
+          <t>39968</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360421</t>
+          <t>359882</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333926</t>
+          <t>335731</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>355828</t>
+          <t>355376</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>698925</t>
+          <t>698831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>720411</t>
+          <t>720397</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24353</t>
+          <t>24867</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26988</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518036</t>
+          <t>517522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534505</t>
+          <t>533927</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159282</t>
+          <t>159449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166890</t>
+          <t>166885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>683183</t>
+          <t>682474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>700068</t>
+          <t>699180</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19825</t>
+          <t>19811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43228</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20583</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41551</t>
+          <t>40491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44291</t>
+          <t>44292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76317</t>
+          <t>76069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1195106</t>
+          <t>1195581</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1218509</t>
+          <t>1218523</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>672734</t>
+          <t>673794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>693702</t>
+          <t>694117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1876303</t>
+          <t>1876551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1908329</t>
+          <t>1908328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11746</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30923</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36333</t>
+          <t>35973</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>337791</t>
+          <t>337211</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347665</t>
+          <t>347432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>537829</t>
+          <t>537952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>556370</t>
+          <t>557289</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>881956</t>
+          <t>882316</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>902024</t>
+          <t>901207</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>33868</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61057</t>
+          <t>60974</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69496</t>
+          <t>69904</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284123</t>
+          <t>284039</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>294787</t>
+          <t>294752</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1187703</t>
+          <t>1187786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1214788</t>
+          <t>1214892</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1477464</t>
+          <t>1477056</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1505945</t>
+          <t>1505281</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61148</t>
+          <t>59995</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97292</t>
+          <t>97033</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113163</t>
+          <t>111518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157795</t>
+          <t>159036</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>183915</t>
+          <t>184000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>240965</t>
+          <t>238905</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3171880</t>
+          <t>3172139</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3208024</t>
+          <t>3209177</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3220329</t>
+          <t>3219088</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3264961</t>
+          <t>3266606</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6406331</t>
+          <t>6408391</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6463381</t>
+          <t>6463296</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28174</t>
+          <t>27732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>26735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26046</t>
+          <t>25807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49511</t>
+          <t>48794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409037</t>
+          <t>409479</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425659</t>
+          <t>426405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285981</t>
+          <t>286632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302544</t>
+          <t>302602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>701066</t>
+          <t>701783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>724531</t>
+          <t>724770</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32427</t>
+          <t>30661</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33458</t>
+          <t>35377</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>30376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58055</t>
+          <t>59367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384591</t>
+          <t>386357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>405876</t>
+          <t>406185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>301857</t>
+          <t>299938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>319781</t>
+          <t>320433</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694278</t>
+          <t>692966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>723032</t>
+          <t>721957</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>32903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>21413</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23319</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48940</t>
+          <t>47636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>592043</t>
+          <t>593435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614035</t>
+          <t>614283</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>236339</t>
+          <t>236525</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250726</t>
+          <t>250588</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>835336</t>
+          <t>836640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>860957</t>
+          <t>860865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39890</t>
+          <t>40961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41849</t>
+          <t>41664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73041</t>
+          <t>73563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65144</t>
+          <t>64335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103606</t>
+          <t>102168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1117425</t>
+          <t>1116354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1139408</t>
+          <t>1139480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>693616</t>
+          <t>693094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>724808</t>
+          <t>724993</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1820367</t>
+          <t>1821805</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1858829</t>
+          <t>1859638</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25387</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20775</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44161</t>
+          <t>42810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33847</t>
+          <t>33417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60518</t>
+          <t>62054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>485209</t>
+          <t>486163</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502212</t>
+          <t>502117</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>714207</t>
+          <t>715558</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>737593</t>
+          <t>737467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1208446</t>
+          <t>1206910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1235117</t>
+          <t>1235547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>27051</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41036</t>
+          <t>41223</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70221</t>
+          <t>71752</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56961</t>
+          <t>56329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90219</t>
+          <t>90311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239346</t>
+          <t>238790</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256126</t>
+          <t>256918</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1035035</t>
+          <t>1033504</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1064220</t>
+          <t>1064033</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1280879</t>
+          <t>1280787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1314137</t>
+          <t>1314769</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92705</t>
+          <t>94352</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140226</t>
+          <t>141282</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>171851</t>
+          <t>170087</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>225421</t>
+          <t>226193</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>275536</t>
+          <t>276535</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>347986</t>
+          <t>350802</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3274093</t>
+          <t>3273037</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3321614</t>
+          <t>3319967</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3311481</t>
+          <t>3310709</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3365051</t>
+          <t>3366815</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6603235</t>
+          <t>6600419</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6675685</t>
+          <t>6674686</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27467</t>
+          <t>27543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22070</t>
+          <t>20989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45430</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404351</t>
+          <t>404102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420471</t>
+          <t>419826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319588</t>
+          <t>319512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337400</t>
+          <t>336897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730717</t>
+          <t>731471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>754077</t>
+          <t>755158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>24505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>29819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>24259</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46474</t>
+          <t>48144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354899</t>
+          <t>352722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>369637</t>
+          <t>369609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341479</t>
+          <t>342454</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359564</t>
+          <t>359250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703026</t>
+          <t>701356</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725950</t>
+          <t>725241</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21873</t>
+          <t>23151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22691</t>
+          <t>22910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37717</t>
+          <t>37672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>500041</t>
+          <t>498763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515475</t>
+          <t>514989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143432</t>
+          <t>143213</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158260</t>
+          <t>158436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650319</t>
+          <t>650364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670577</t>
+          <t>671045</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18333</t>
+          <t>18077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40105</t>
+          <t>39572</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>37087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66432</t>
+          <t>65147</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61552</t>
+          <t>62541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97974</t>
+          <t>96984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1109533</t>
+          <t>1110066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1131305</t>
+          <t>1131561</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>759444</t>
+          <t>760729</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>788756</t>
+          <t>788789</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1877540</t>
+          <t>1878530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1913962</t>
+          <t>1912973</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12408</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30133</t>
+          <t>30839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27335</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53299</t>
+          <t>51256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44186</t>
+          <t>46308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75113</t>
+          <t>79228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>590573</t>
+          <t>589867</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>608298</t>
+          <t>607151</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>684945</t>
+          <t>686988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710909</t>
+          <t>710736</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1283837</t>
+          <t>1279722</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1314764</t>
+          <t>1312642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23575</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36954</t>
+          <t>37872</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66659</t>
+          <t>67781</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50066</t>
+          <t>50014</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81814</t>
+          <t>81304</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263570</t>
+          <t>263857</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279388</t>
+          <t>279349</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1015366</t>
+          <t>1014244</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1045071</t>
+          <t>1044153</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1287356</t>
+          <t>1287866</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1319104</t>
+          <t>1319156</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85870</t>
+          <t>84813</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128308</t>
+          <t>127933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163757</t>
+          <t>165109</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>219150</t>
+          <t>220938</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>261074</t>
+          <t>260618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>329811</t>
+          <t>328514</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3257414</t>
+          <t>3257789</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3299852</t>
+          <t>3300909</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3312446</t>
+          <t>3310658</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3367839</t>
+          <t>3366487</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6587507</t>
+          <t>6588804</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6656244</t>
+          <t>6656700</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8594</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30402</t>
+          <t>30410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>18331</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36204</t>
+          <t>37289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41184</t>
+          <t>44179</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29821</t>
+          <t>32352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56324</t>
+          <t>59132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>488674</t>
+          <t>533543</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>474810</t>
+          <t>520208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>496618</t>
+          <t>541467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>422821</t>
+          <t>461307</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>411263</t>
+          <t>451122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430365</t>
+          <t>470080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>911495</t>
+          <t>994850</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>896355</t>
+          <t>979897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>922858</t>
+          <t>1006677</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,17 +8976,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25433</t>
+          <t>26810</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28473</t>
+          <t>31710</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20521</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40012</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,22 +9046,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>43485</t>
+          <t>47775</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33033</t>
+          <t>35870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57513</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -9089,17 +9089,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>437201</t>
+          <t>467146</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>426780</t>
+          <t>456402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443534</t>
+          <t>472908</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>354107</t>
+          <t>391433</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342568</t>
+          <t>380717</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362059</t>
+          <t>400662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,27 +9159,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>791308</t>
+          <t>858580</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>777280</t>
+          <t>844813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>801760</t>
+          <t>870485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18739</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>12085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36863</t>
+          <t>31453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14270</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27768</t>
+          <t>30868</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45091</t>
+          <t>43185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>649525</t>
+          <t>451073</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631401</t>
+          <t>440159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662980</t>
+          <t>459527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>157882</t>
+          <t>177168</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152641</t>
+          <t>170109</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161665</t>
+          <t>181309</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>807407</t>
+          <t>628241</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>790084</t>
+          <t>615924</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>823220</t>
+          <t>638058</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29451</t>
+          <t>34900</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45253</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35699</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>30231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50501</t>
+          <t>49985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>65151</t>
+          <t>74784</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43790</t>
+          <t>59322</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83226</t>
+          <t>93684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1005368</t>
+          <t>1096943</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>989566</t>
+          <t>1084170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1014628</t>
+          <t>1109052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>941498</t>
+          <t>820400</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>926696</t>
+          <t>810299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>960563</t>
+          <t>830053</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1946865</t>
+          <t>1917343</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1928790</t>
+          <t>1898443</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1968226</t>
+          <t>1932805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28725</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>98985</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28917</t>
+          <t>29077</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>294043</t>
+          <t>49824</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>117767</t>
+          <t>58305</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47258</t>
+          <t>46334</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>308002</t>
+          <t>72974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>454777</t>
+          <t>547100</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>444834</t>
+          <t>536007</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462655</t>
+          <t>554153</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>740011</t>
+          <t>791202</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>544953</t>
+          <t>780303</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>810079</t>
+          <t>801050</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1194788</t>
+          <t>1338303</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1004553</t>
+          <t>1323634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1265297</t>
+          <t>1350274</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>17847</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27711</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20009</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40276</t>
+          <t>45719</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37558</t>
+          <t>39195</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26505</t>
+          <t>28045</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56739</t>
+          <t>56056</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>230660</t>
+          <t>229761</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211630</t>
+          <t>219381</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237743</t>
+          <t>234963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>732441</t>
+          <t>811265</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>719876</t>
+          <t>797274</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>740143</t>
+          <t>821471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>963101</t>
+          <t>1041026</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>943920</t>
+          <t>1024165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>974154</t>
+          <t>1052176</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>108369</t>
+          <t>115428</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78842</t>
+          <t>94850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139397</t>
+          <t>142524</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,67 +10726,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>224543</t>
+          <t>179679</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148888</t>
+          <t>156347</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>485790</t>
+          <t>204416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>295107</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>262879</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>327736</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>332912</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>250852</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>633255</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3266205</t>
+          <t>3325565</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3235177</t>
+          <t>3298469</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3295732</t>
+          <t>3346143</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,67 +10839,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3348760</t>
+          <t>3452776</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3087513</t>
+          <t>3428039</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3424415</t>
+          <t>3476108</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>8196</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6778342</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6745713</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6810570</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>95,83%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>8196</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6614965</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6314622</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6697025</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
